--- a/output/pdf_financials_xlsx/IZN.xlsx
+++ b/output/pdf_financials_xlsx/IZN.xlsx
@@ -1037,40 +1037,40 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.072575</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.007195</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.004382</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.006081</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.004846</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.005454</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.001886</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.007092</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.0037</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.001422</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.002157</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
@@ -2005,40 +2005,40 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.334527</v>
+        <v>-0.261952</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.434691</v>
+        <v>-0.427496</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.633014</v>
+        <v>-0.637396</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.480567</v>
+        <v>-0.486648</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.504601</v>
+        <v>-0.509447</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.391591</v>
+        <v>-0.397045</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.525732</v>
+        <v>-0.527618</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.248571</v>
+        <v>-0.255663</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.495357</v>
+        <v>-0.499057</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.600585</v>
+        <v>-0.602007</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-0.46246</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.227758</v>
+        <v>-0.229915</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>3.271177</v>
@@ -2121,40 +2121,40 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.334527</v>
+        <v>-0.261952</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.434691</v>
+        <v>-0.427496</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.633014</v>
+        <v>-0.637396</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.480567</v>
+        <v>-0.486648</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.504601</v>
+        <v>-0.509447</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.391591</v>
+        <v>-0.397045</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.525732</v>
+        <v>-0.527618</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.248571</v>
+        <v>-0.255663</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.495357</v>
+        <v>-0.499057</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.600585</v>
+        <v>-0.602007</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-0.46246</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.227758</v>
+        <v>-0.229915</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>3.271177</v>
@@ -2434,40 +2434,40 @@
         <v>1.24244</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.24244</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.754903</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.704579</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.350771</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.153325</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.784188</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.482729</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>3.483198</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.59762</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.431146</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>3.165251</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.464808</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>1.617659</v>
@@ -2550,40 +2550,40 @@
         <v>1.247913</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.005473</v>
+        <v>1.247913</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.01117</v>
+        <v>0.766073</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.003125</v>
+        <v>0.707704</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.002047</v>
+        <v>0.352818</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.001603</v>
+        <v>1.154928</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.000957</v>
+        <v>0.785145</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.001874</v>
+        <v>0.484603</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.001665</v>
+        <v>3.484863</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.00077</v>
+        <v>0.59839</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.000291</v>
+        <v>0.431437</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>1.110646</v>
+        <v>4.275897</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>1.328076</v>
+        <v>2.792884</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>2.560205</v>
@@ -3246,40 +3246,40 @@
         <v>0.008845</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.251285</v>
+        <v>0.008845</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.7624</v>
+        <v>0.007497</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.718964</v>
+        <v>0.014385</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.364889</v>
+        <v>0.014118</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.167392</v>
+        <v>0.014067</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.798332</v>
+        <v>0.014144</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.496599</v>
+        <v>0.01387</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>3.498998</v>
+        <v>0.0158</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.617494</v>
+        <v>0.019874</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.449378</v>
+        <v>0.018232</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>3.184393</v>
+        <v>0.019142</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.482435</v>
+        <v>0.017627</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0.0258</v>
@@ -9202,7 +9202,11 @@
           <t>Reclamation deposits (Note 6)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -9855,7 +9859,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -10114,7 +10118,11 @@
           <t>Reclamation deposits (Note 7)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -10763,7 +10771,11 @@
           <t>Reclamation deposit (Note 7)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -11640,7 +11652,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -12258,7 +12270,11 @@
           <t>Reclamation deposit (Note 7) 77,035</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -14183,7 +14199,11 @@
           <t>Reclamation Deposit</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E58" s="5" t="n">
         <v>0.050624</v>
       </c>
@@ -15923,7 +15943,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -18085,7 +18109,11 @@
           <t>Unrealized foreign exchange loss (gain) on reclamation deposit</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -18487,7 +18515,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -19293,7 +19325,11 @@
           <t>Unrealized foreign exchange loss on reclamation deposit</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -20394,7 +20430,11 @@
           <t>Unrealized foreign exchange gain (loss) on reclamation deposit</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -21372,7 +21412,11 @@
           <t>Unrealized foreign exchange gain on reclamation deposit</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -21960,7 +22004,11 @@
           <t>Unrealized foreign exchange loss (gain) on reclamation deposit</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -23596,7 +23644,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E153" s="5" t="n">
         <v>-0.00674</v>
       </c>
@@ -33748,7 +33800,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -43770,7 +43822,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -45000,7 +45052,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E367" s="5" t="n">

--- a/output/pdf_financials_xlsx/IZN.xlsx
+++ b/output/pdf_financials_xlsx/IZN.xlsx
@@ -792,10 +792,10 @@
         <v>0.118065</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.138714</v>
+        <v>0.170511</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.110991</v>
+        <v>0.143633</v>
       </c>
     </row>
     <row r="8">
@@ -4471,28 +4471,28 @@
         <v>0</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.031674</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.02758</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.0275</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.0275</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.028192</v>
       </c>
     </row>
     <row r="68">
@@ -7383,13 +7383,13 @@
         <v>0</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.714974</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>0.476848</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>0.033404</v>
       </c>
     </row>
     <row r="116">
@@ -16040,7 +16040,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -17535,7 +17539,11 @@
           <t>Proceeds from share issue</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -21713,7 +21721,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -27185,7 +27197,11 @@
           <t>Director fees (Note 10)</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
